--- a/outputs/marine_equipment/Раскладка_клинкетов.xlsx
+++ b/outputs/marine_equipment/Раскладка_клинкетов.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Справочник габаритов" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Усиленный 27 т" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Контейнер 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Контейнер 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочник габаритов" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Усиленный 27 т" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Контейнер 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Контейнер 2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="9" t="inlineStr"/>
       <c r="D10" s="9" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>0.45</v>
